--- a/artfynd/A 20798-2019 artfynd.xlsx
+++ b/artfynd/A 20798-2019 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121344485</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20798-2019 artfynd.xlsx
+++ b/artfynd/A 20798-2019 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121344485</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20798-2019 artfynd.xlsx
+++ b/artfynd/A 20798-2019 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121344485</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20798-2019 artfynd.xlsx
+++ b/artfynd/A 20798-2019 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121344485</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20798-2019 artfynd.xlsx
+++ b/artfynd/A 20798-2019 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121344485</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20798-2019 artfynd.xlsx
+++ b/artfynd/A 20798-2019 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121344485</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
